--- a/financials/MBB/MBB_Q.xlsx
+++ b/financials/MBB/MBB_Q.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12000" yWindow="5520" windowWidth="12000" windowHeight="7380" tabRatio="600" firstSheet="3" activeTab="4" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="4545" windowWidth="24000" windowHeight="8355" tabRatio="600" firstSheet="3" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,10 +13,6 @@
     <sheet name="Dự báo tăng trưởng" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Hiệu quả thực hiện kế hoạch" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-    <externalReference r:id="rId8"/>
-  </externalReferences>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -313,7 +309,7 @@
     <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -367,22 +363,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFF0000"/>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -457,63 +437,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="B2">
-            <v>26650</v>
-          </cell>
-          <cell r="G2">
-            <v>75100</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
-    <sheetNames>
-      <sheetName val="CĐKT"/>
-      <sheetName val="KQHĐKD"/>
-      <sheetName val="LCTT"/>
-      <sheetName val="Phân tích"/>
-      <sheetName val="Dự báo tăng trưởng"/>
-      <sheetName val="Hiệu quả thực hiện KH"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="18">
-          <cell r="C18">
-            <v>22729</v>
-          </cell>
-          <cell r="D18">
-            <v>26306</v>
-          </cell>
-          <cell r="E18">
-            <v>28829</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10113,12 +10036,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="55.75" bestFit="1" customWidth="1" style="11" min="1" max="1"/>
-    <col width="7.875" customWidth="1" style="11" min="2" max="9"/>
-    <col width="20.625" bestFit="1" customWidth="1" style="11" min="10" max="10"/>
+    <col width="47.875" bestFit="1" customWidth="1" style="11" min="1" max="1"/>
+    <col width="17.125" bestFit="1" customWidth="1" style="11" min="2" max="7"/>
+    <col width="18.125" bestFit="1" customWidth="1" style="11" min="8" max="10"/>
     <col width="9" customWidth="1" style="11" min="11" max="16384"/>
   </cols>
   <sheetData>
@@ -12182,6 +12105,45 @@
       </c>
       <c r="J61" s="35" t="n">
         <v>30415000000000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>Tổng lợi nhuận/lỗ trước thuế</t>
+        </is>
+      </c>
+      <c r="B62" s="35">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng lợi nhuận/lỗ trước thuế",income_statement!$A:$A,0),MATCH(B$21,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C62" s="35">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng lợi nhuận/lỗ trước thuế",income_statement!$A:$A,0),MATCH(C$21,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D62" s="35">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng lợi nhuận/lỗ trước thuế",income_statement!$A:$A,0),MATCH(D$21,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E62" s="35">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng lợi nhuận/lỗ trước thuế",income_statement!$A:$A,0),MATCH(E$21,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F62" s="35">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng lợi nhuận/lỗ trước thuế",income_statement!$A:$A,0),MATCH(F$21,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G62" s="35">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng lợi nhuận/lỗ trước thuế",income_statement!$A:$A,0),MATCH(G$21,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H62" s="35">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng lợi nhuận/lỗ trước thuế",income_statement!$A:$A,0),MATCH(H$21,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I62" s="35">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng lợi nhuận/lỗ trước thuế",income_statement!$A:$A,0),MATCH(I$21,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -12276,25 +12238,20 @@
           <t>Thị giá</t>
         </is>
       </c>
-      <c r="B3" s="12">
-        <f>[1]Sheet1!$G$2</f>
-        <v/>
-      </c>
-      <c r="C3" s="12">
-        <f>[1]Sheet1!$G$2</f>
-        <v/>
-      </c>
-      <c r="D3" s="12">
-        <f>[1]Sheet1!$G$2</f>
-        <v/>
-      </c>
-      <c r="E3" s="12">
-        <f>[1]Sheet1!$G$2</f>
-        <v/>
-      </c>
-      <c r="F3" s="12">
-        <f>[1]Sheet1!$G$2</f>
-        <v/>
+      <c r="B3" s="12" t="n">
+        <v>75100</v>
+      </c>
+      <c r="C3" s="12" t="n">
+        <v>75100</v>
+      </c>
+      <c r="D3" s="12" t="n">
+        <v>75100</v>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>75100</v>
+      </c>
+      <c r="F3" s="12" t="n">
+        <v>75100</v>
       </c>
     </row>
     <row r="4">
@@ -12532,15 +12489,15 @@
         </is>
       </c>
       <c r="B3" s="12">
-        <f>[2]KQHĐKD!C18*1000</f>
+        <f>chi_so_tai_chinh!F62/1000000</f>
         <v/>
       </c>
       <c r="C3" s="12">
-        <f>[2]KQHĐKD!D18*1000</f>
+        <f>chi_so_tai_chinh!G62/1000000</f>
         <v/>
       </c>
       <c r="D3" s="12">
-        <f>[2]KQHĐKD!E18*1000</f>
+        <f>chi_so_tai_chinh!H62/1000000</f>
         <v/>
       </c>
       <c r="E3" s="12" t="n"/>
@@ -12590,6 +12547,11 @@
   </sheetData>
   <conditionalFormatting sqref="B6">
     <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="0">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12598,11 +12560,6 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
-    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>